--- a/tests/fixtures/expected/gruppen_veranstaltungen.xlsx
+++ b/tests/fixtures/expected/gruppen_veranstaltungen.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[dates]2026-09-06 00:00:00 bis 2026-09-06 23:59:59</t>
+          <t>[dates]2026-09-06 00:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
